--- a/safety_inspection_forms/011_dormitory_safety_inspection_form--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/011_dormitory_safety_inspection_form--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1466,51 +1466,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>electrical_hazards_choices</t>
+          <t>fire_hazards_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no_electrical_outlet_or_socket</t>
+          <t>no_hazardous_fire_equipment_present</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No electrical outlet or socket</t>
+          <t>No hazardous fire equipment present</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>electrical_hazards_choices</t>
+          <t>fire_hazards_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no_electrical_cord</t>
+          <t>no_fire_equipment_with_frayed_or_exposed_wiring</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No electrical cord</t>
+          <t>No fire equipment with frayed or exposed wiring</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>electrical_hazards_choices</t>
+          <t>fire_hazards_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no_electrical_box</t>
+          <t>no_exposed_fire_equipment</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No electrical box</t>
+          <t>No exposed fire equipment</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no_hazardous_fire_equipment_present</t>
+          <t>no_fire_alarm_system</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No hazardous fire equipment present</t>
+          <t>No fire alarm system</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>no_fire_equipment_with_frayed_or_exposed_wiring</t>
+          <t>no_fire_exit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No fire equipment with frayed or exposed wiring</t>
+          <t>No fire exit</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no_exposed_fire_equipment</t>
+          <t>no_fire_hydrant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No exposed fire equipment</t>
+          <t>No fire hydrant</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>no_fire_alarm_system</t>
+          <t>no_fire_alarm_pull_station</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No fire alarm system</t>
+          <t>No fire alarm pull station</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no_fire_exit</t>
+          <t>no_fire_hose</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No fire exit</t>
+          <t>No fire hose</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>no_fire_hydrant</t>
+          <t>no_fire_hose_cabinet</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>No fire hydrant</t>
+          <t>No fire hose cabinet</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no_fire_alarm_pull_station</t>
+          <t>no_fire_extinguisher_cabinet</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No fire alarm pull station</t>
+          <t>No fire extinguisher cabinet</t>
         </is>
       </c>
     </row>
@@ -1641,63 +1641,63 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>no_fire_hose</t>
+          <t>no_fire_safety_poster</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No fire hose</t>
+          <t>No fire safety poster</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>fire_hazards_choices</t>
+          <t>medical_hazards_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no_fire_hose_cabinet</t>
+          <t>no_hazardous_medical_equipment_present</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No fire hose cabinet</t>
+          <t>No hazardous medical equipment present</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fire_hazards_choices</t>
+          <t>medical_hazards_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>no_fire_extinguisher_cabinet</t>
+          <t>no_sharps_or_needles</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No fire extinguisher cabinet</t>
+          <t>No sharps or needles</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>fire_hazards_choices</t>
+          <t>medical_hazards_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no_fire_safety_poster</t>
+          <t>no_broken_or_loose_medical_equipment</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No fire safety poster</t>
+          <t>No broken or loose medical equipment</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>no_hazardous_medical_equipment_present</t>
+          <t>no_biohazard_label</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No hazardous medical equipment present</t>
+          <t>No biohazard label</t>
         </is>
       </c>
     </row>
@@ -1726,63 +1726,63 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>no_sharps_or_needles</t>
+          <t>no_chemical_or_biological_waste</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No sharps or needles</t>
+          <t>No chemical or biological waste</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>medical_hazards_choices</t>
+          <t>structural_hazards_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>no_broken_or_loose_medical_equipment</t>
+          <t>no_structural_damage_or_hazards</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No broken or loose medical equipment</t>
+          <t>No structural damage or hazards</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>medical_hazards_choices</t>
+          <t>structural_hazards_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>no_biohazard_label</t>
+          <t>no_uneven_or_sagging_floor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No biohazard label</t>
+          <t>No uneven or sagging floor</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>medical_hazards_choices</t>
+          <t>structural_hazards_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>no_chemical_or_biological_waste</t>
+          <t>no_uneven_or_sagging_ceiling</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No chemical or biological waste</t>
+          <t>No uneven or sagging ceiling</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>no_structural_damage_or_hazards</t>
+          <t>no_uneven_or_sagging_roof</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No structural damage or hazards</t>
+          <t>No uneven or sagging roof</t>
         </is>
       </c>
     </row>
@@ -1811,63 +1811,63 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>no_uneven_or_sagging_floor</t>
+          <t>no_uneven_or_sagging_floor_joist</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>No uneven or sagging floor</t>
+          <t>No uneven or sagging floor joist</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>structural_hazards_choices</t>
+          <t>environmental_hazards_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>no_uneven_or_sagging_ceiling</t>
+          <t>no_hazardous_chemicals_or_substances_present</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>No uneven or sagging ceiling</t>
+          <t>No hazardous chemicals or substances present</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>structural_hazards_choices</t>
+          <t>environmental_hazards_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>no_uneven_or_sagging_roof</t>
+          <t>no_mold_or_mildew</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>No uneven or sagging roof</t>
+          <t>No mold or mildew</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>structural_hazards_choices</t>
+          <t>environmental_hazards_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>no_uneven_or_sagging_floor_joist</t>
+          <t>no_pest_or_rodent_infestation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>No uneven or sagging floor joist</t>
+          <t>No pest or rodent infestation</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>no_hazardous_chemicals_or_substances_present</t>
+          <t>no_unusual_odors_or_smells</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No hazardous chemicals or substances present</t>
+          <t>No unusual odors or smells</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>no_mold_or_mildew</t>
+          <t>no_standing_water</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No mold or mildew</t>
+          <t>No standing water</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>no_pest_or_rodent_infestation</t>
+          <t>no_slippery_floor</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>No pest or rodent infestation</t>
+          <t>No slippery floor</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>no_unusual_odors_or_smells</t>
+          <t>no_broken_or_leaky_faucets</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No unusual odors or smells</t>
+          <t>No broken or leaky faucets</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>no_standing_water</t>
+          <t>no_exposed_wiring</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>No standing water</t>
+          <t>No exposed wiring</t>
         </is>
       </c>
     </row>
@@ -1964,61 +1964,10 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>no_slippery_floor</t>
+          <t>no_exposed_pipes</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
-        <is>
-          <t>No slippery floor</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>environmental_hazards_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>no_broken_or_leaky_faucets</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>No broken or leaky faucets</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>environmental_hazards_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>no_exposed_wiring</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>No exposed wiring</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>environmental_hazards_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>no_exposed_pipes</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
         <is>
           <t>No exposed pipes</t>
         </is>
